--- a/review_data/ruler/inputs/2026-10-11_trigger_workbook_with_claude_appends.xlsx
+++ b/review_data/ruler/inputs/2026-10-11_trigger_workbook_with_claude_appends.xlsx
@@ -3997,7 +3997,7 @@
       </c>
       <c r="C6" s="65" t="inlineStr">
         <is>
-          <t>I did not open any link. A few entries need checking by Mr. Advocate before anyone relies on them: 'Hitesh Verma v. State of Uttarakhand' is given as Uttarakhand High Court, 20 Jul 2020 (the widely cited decision on 'within public view' is the Supreme Court's, later in 2020; the sheet may be citing the High Court order under appeal) [Likely]; 'N. Mahesh v. G.N. Nanjundaswamy' is dated 14 Aug 2026 with the court given only as 'Indian court'; the ITPA row cites a search-results page, not a judgment; the Motor Vehicles row cites the statute page twice; several 2026 items are unverified. None of this changes the words we would use; it matters if the sheet is quoted as authority.</t>
+          <t>I did not open any link. CORRECTED 2026-10-12 after Mr. Advocate's review: 'Hitesh Verma v. State of Uttarakhand' is an SC/ST Act case that went on appeal to the Supreme Court and the Supreme Court's decision (5 Nov 2020) is a landmark SC/ST Act judgment; it is in our index. The sheet's row cites the earlier High Court stage; it should cite the Supreme Court decision. My earlier suggestion that this was a mislabelled court was too strong. 'N. Mahesh v. G.N. Nanjundaswamy' is a Bangalore District Court order of 14 Aug 2026 (Mr. Advocate); it is a trial-court order, not binding precedent, and is not in our Supreme Court index; it is illustrative only. Still open: the ITPA row cites a search-results page, not a judgment; the Motor Vehicles row cites the statute page twice. None of this changes the words we would use; it matters if the sheet is quoted as authority.</t>
         </is>
       </c>
       <c r="D6" s="65" t="inlineStr">
